--- a/Sum_Results.xlsx
+++ b/Sum_Results.xlsx
@@ -62,11 +62,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -422,7 +423,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -434,19 +435,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -631,7 +619,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -643,34 +631,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -755,7 +743,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -771,28 +759,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1328,7 +1337,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="15.8181818181818" customWidth="1"/>
@@ -1337,6 +1346,8 @@
     <col min="7" max="7" width="19.2727272727273" customWidth="1"/>
     <col min="9" max="9" width="20.3636363636364" customWidth="1"/>
     <col min="10" max="10" width="23.8181818181818" customWidth="1"/>
+    <col min="12" max="12" width="20.7272727272727" customWidth="1"/>
+    <col min="13" max="13" width="23.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1346,60 +1357,60 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
       <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="4" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1"/>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="10" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1407,286 +1418,286 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
       <c r="C3" s="1">
         <v>5.954</v>
       </c>
-      <c r="D3" s="7">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
         <v>1</v>
       </c>
       <c r="F3" s="1">
         <v>4.923</v>
       </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3" s="1">
         <v>1.752</v>
       </c>
-      <c r="J3" s="7">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>0.372</v>
-      </c>
-      <c r="M3">
-        <v>0.58</v>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+      <c r="L3" s="12">
+        <v>1.673</v>
+      </c>
+      <c r="M3" s="13">
+        <v>0.578751550227367</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="1">
         <v>3.593</v>
       </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
         <v>1</v>
       </c>
       <c r="F4" s="1">
         <v>3.85</v>
       </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
         <v>1</v>
       </c>
       <c r="I4" s="1">
         <v>3.08</v>
       </c>
-      <c r="J4" s="7">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>0.858</v>
-      </c>
-      <c r="M4">
-        <v>0.12</v>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="11">
+        <v>1</v>
+      </c>
+      <c r="L4" s="12">
+        <v>3.164</v>
+      </c>
+      <c r="M4" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>1</v>
       </c>
       <c r="C5" s="1">
         <v>1.215</v>
       </c>
-      <c r="D5" s="7">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
         <v>1</v>
       </c>
       <c r="F5" s="1">
         <v>1.096</v>
       </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
         <v>1</v>
       </c>
       <c r="I5" s="1">
         <v>0.22</v>
       </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>0.173</v>
-      </c>
-      <c r="M5">
-        <v>2.23</v>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11">
+        <v>1</v>
+      </c>
+      <c r="L5" s="12">
+        <v>0.318</v>
+      </c>
+      <c r="M5" s="13">
+        <v>2.22902097902098</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>1</v>
       </c>
       <c r="C6" s="1">
         <v>3.034</v>
       </c>
-      <c r="D6" s="7">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
         <v>1</v>
       </c>
       <c r="F6" s="1">
         <v>3.786</v>
       </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
         <v>1</v>
       </c>
       <c r="I6" s="1">
         <v>3.513</v>
       </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>0.314</v>
-      </c>
-      <c r="M6">
-        <v>1.15</v>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11">
+        <v>1</v>
+      </c>
+      <c r="L6" s="12">
+        <v>1.566</v>
+      </c>
+      <c r="M6" s="13">
+        <v>1.15440115440115</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>1</v>
       </c>
       <c r="C7" s="1">
         <v>0.861</v>
       </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
         <v>1</v>
       </c>
       <c r="F7" s="1">
         <v>0.847</v>
       </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
         <v>1</v>
       </c>
       <c r="I7" s="1">
         <v>1.142</v>
       </c>
-      <c r="J7" s="7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>0.107</v>
-      </c>
-      <c r="M7">
-        <v>2.71</v>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="11">
+        <v>1</v>
+      </c>
+      <c r="L7" s="12">
+        <v>0.339</v>
+      </c>
+      <c r="M7" s="13">
+        <v>2.70802560315116</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>1</v>
       </c>
       <c r="C8" s="1">
         <v>4.641</v>
       </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
         <v>1</v>
       </c>
       <c r="F8" s="1">
         <v>2.778</v>
       </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
         <v>1</v>
       </c>
       <c r="I8" s="1">
         <v>4.213</v>
       </c>
-      <c r="J8" s="7">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>0.675</v>
-      </c>
-      <c r="M8">
-        <v>0.1</v>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11">
+        <v>1</v>
+      </c>
+      <c r="L8" s="12">
+        <v>3.542</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0.0963391136801541</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>1</v>
       </c>
       <c r="C9" s="1">
         <v>0.715</v>
       </c>
-      <c r="D9" s="7">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
         <v>1</v>
       </c>
       <c r="F9" s="1">
         <v>0.826</v>
       </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
         <v>1</v>
       </c>
       <c r="I9" s="1">
         <v>0.151</v>
       </c>
-      <c r="J9" s="7">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>0.174</v>
-      </c>
-      <c r="M9">
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="11">
+        <v>1</v>
+      </c>
+      <c r="L9" s="12">
+        <v>0.326</v>
+      </c>
+      <c r="M9" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1694,40 +1705,40 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>1</v>
       </c>
       <c r="C10" s="1">
         <v>2.744</v>
       </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
         <v>1</v>
       </c>
       <c r="F10" s="1">
         <v>5.548</v>
       </c>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6">
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
         <v>1</v>
       </c>
       <c r="I10" s="1">
         <v>1.779</v>
       </c>
-      <c r="J10" s="7">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>0.185</v>
-      </c>
-      <c r="M10">
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11">
+        <v>1</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0.811</v>
+      </c>
+      <c r="M10" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1735,286 +1746,286 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>1</v>
       </c>
       <c r="C11" s="1">
         <v>4.121</v>
       </c>
-      <c r="D11" s="7">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
         <v>1</v>
       </c>
       <c r="F11" s="1">
         <v>4.197</v>
       </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
         <v>1</v>
       </c>
       <c r="I11" s="1">
         <v>3.063</v>
       </c>
-      <c r="J11" s="7">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>0.325</v>
-      </c>
-      <c r="M11">
-        <v>1.45</v>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="11">
+        <v>1</v>
+      </c>
+      <c r="L11" s="12">
+        <v>1.542</v>
+      </c>
+      <c r="M11" s="13">
+        <v>1.44609991235758</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>1</v>
       </c>
       <c r="C12" s="1">
         <v>1.429</v>
       </c>
-      <c r="D12" s="7">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
         <v>1</v>
       </c>
       <c r="F12" s="1">
         <v>1.739</v>
       </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
         <v>1</v>
       </c>
       <c r="I12" s="1">
         <v>1.357</v>
       </c>
-      <c r="J12" s="7">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>0.281</v>
-      </c>
-      <c r="M12">
-        <v>0.51</v>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="11">
+        <v>1</v>
+      </c>
+      <c r="L12" s="12">
+        <v>1.239</v>
+      </c>
+      <c r="M12" s="13">
+        <v>0.514444004748714</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>1</v>
       </c>
       <c r="C13" s="1">
         <v>1.681</v>
       </c>
-      <c r="D13" s="7">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
         <v>1</v>
       </c>
       <c r="F13" s="1">
         <v>1.397</v>
       </c>
-      <c r="G13" s="7">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6">
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
         <v>1</v>
       </c>
       <c r="I13" s="1">
         <v>1.298</v>
       </c>
-      <c r="J13" s="7">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>0.267</v>
-      </c>
-      <c r="M13">
-        <v>0.57</v>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11">
+        <v>1</v>
+      </c>
+      <c r="L13" s="12">
+        <v>1.31</v>
+      </c>
+      <c r="M13" s="13">
+        <v>0.570206699928724</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>1</v>
       </c>
       <c r="C14" s="1">
         <v>0.81</v>
       </c>
-      <c r="D14" s="7">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
         <v>1</v>
       </c>
       <c r="F14" s="1">
         <v>0.793</v>
       </c>
-      <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6">
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
         <v>1</v>
       </c>
       <c r="I14" s="1">
         <v>0.746</v>
       </c>
-      <c r="J14" s="7">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>0.138</v>
-      </c>
-      <c r="M14">
-        <v>2.11</v>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11">
+        <v>1</v>
+      </c>
+      <c r="L14" s="12">
+        <v>0.361</v>
+      </c>
+      <c r="M14" s="13">
+        <v>2.10832424572883</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>1</v>
       </c>
       <c r="C15" s="1">
         <v>1.579</v>
       </c>
-      <c r="D15" s="7">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
         <v>1</v>
       </c>
       <c r="F15" s="1">
         <v>1.539</v>
       </c>
-      <c r="G15" s="7">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
         <v>1</v>
       </c>
       <c r="I15" s="1">
         <v>2.504</v>
       </c>
-      <c r="J15" s="7">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>0.165</v>
-      </c>
-      <c r="M15">
-        <v>2.37</v>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="11">
+        <v>1</v>
+      </c>
+      <c r="L15" s="12">
+        <v>0.292</v>
+      </c>
+      <c r="M15" s="13">
+        <v>2.3728813559322</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="4">
         <v>1</v>
       </c>
       <c r="C16" s="1">
         <v>0.3</v>
       </c>
-      <c r="D16" s="7">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
         <v>1</v>
       </c>
       <c r="F16" s="1">
         <v>0.291</v>
       </c>
-      <c r="G16" s="7">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6">
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
         <v>1</v>
       </c>
       <c r="I16" s="1">
         <v>0.338</v>
       </c>
-      <c r="J16" s="7">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>0.046</v>
-      </c>
-      <c r="M16">
-        <v>1.94</v>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="11">
+        <v>1</v>
+      </c>
+      <c r="L16" s="12">
+        <v>0.094</v>
+      </c>
+      <c r="M16" s="13">
+        <v>1.94120909595119</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="4">
         <v>1</v>
       </c>
       <c r="C17" s="1">
         <v>3.498</v>
       </c>
-      <c r="D17" s="7">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
         <v>1</v>
       </c>
       <c r="F17" s="1">
         <v>6.216</v>
       </c>
-      <c r="G17" s="7">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
         <v>1</v>
       </c>
       <c r="I17" s="1">
         <v>5.158</v>
       </c>
-      <c r="J17" s="7">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>1.133</v>
-      </c>
-      <c r="M17">
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="11">
+        <v>1</v>
+      </c>
+      <c r="L17" s="12">
+        <v>6.852</v>
+      </c>
+      <c r="M17" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2022,205 +2033,246 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="4">
         <v>1</v>
       </c>
       <c r="C18" s="1">
         <v>0.876</v>
       </c>
-      <c r="D18" s="7">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
         <v>1</v>
       </c>
       <c r="F18" s="1">
         <v>0.197</v>
       </c>
-      <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6">
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
         <v>1</v>
       </c>
       <c r="I18" s="1">
         <v>1.196</v>
       </c>
-      <c r="J18" s="7">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>0.16</v>
-      </c>
-      <c r="M18">
-        <v>0.82</v>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="11">
+        <v>1</v>
+      </c>
+      <c r="L18" s="12">
+        <v>0.679</v>
+      </c>
+      <c r="M18" s="13">
+        <v>0.822867042009528</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="4">
         <v>1</v>
       </c>
       <c r="C19" s="1">
         <v>4.559</v>
       </c>
-      <c r="D19" s="7">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
         <v>1</v>
       </c>
       <c r="F19" s="1">
         <v>4.79</v>
       </c>
-      <c r="G19" s="7">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6">
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
         <v>1</v>
       </c>
       <c r="I19" s="1">
         <v>3.486</v>
       </c>
-      <c r="J19" s="7">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>0.565</v>
-      </c>
-      <c r="M19">
-        <v>0.87</v>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="11">
+        <v>1</v>
+      </c>
+      <c r="L19" s="12">
+        <v>2.353</v>
+      </c>
+      <c r="M19" s="13">
+        <v>0.866188769414576</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="4">
         <v>1</v>
       </c>
       <c r="C20" s="1">
         <v>1.827</v>
       </c>
-      <c r="D20" s="7">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
         <v>1</v>
       </c>
       <c r="F20" s="1">
         <v>1.744</v>
       </c>
-      <c r="G20" s="7">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6">
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
         <v>1</v>
       </c>
       <c r="I20" s="1">
         <v>1.634</v>
       </c>
-      <c r="J20" s="7">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>0.17</v>
-      </c>
-      <c r="M20">
-        <v>0.53</v>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="11">
+        <v>1</v>
+      </c>
+      <c r="L20" s="12">
+        <v>0.773</v>
+      </c>
+      <c r="M20" s="13">
+        <v>0.532544378698225</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="4">
         <v>1</v>
       </c>
       <c r="C21" s="1">
         <v>6.091</v>
       </c>
-      <c r="D21" s="7">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
         <v>1</v>
       </c>
       <c r="F21" s="1">
         <v>6.007</v>
       </c>
-      <c r="G21" s="7">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
         <v>1</v>
       </c>
       <c r="I21" s="1">
         <v>5.533</v>
       </c>
-      <c r="J21" s="7">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>0.279</v>
-      </c>
-      <c r="M21">
-        <v>0.46</v>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="11">
+        <v>1</v>
+      </c>
+      <c r="L21" s="12">
+        <v>1.575</v>
+      </c>
+      <c r="M21" s="13">
+        <v>0.461361014994233</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="10">
-        <v>1</v>
-      </c>
-      <c r="C22" s="11">
+      <c r="B22" s="14">
+        <v>1</v>
+      </c>
+      <c r="C22" s="15">
         <v>3.357</v>
       </c>
-      <c r="D22" s="12">
-        <v>0</v>
-      </c>
-      <c r="E22" s="10">
-        <v>1</v>
-      </c>
-      <c r="F22" s="11">
+      <c r="D22" s="16">
+        <v>0</v>
+      </c>
+      <c r="E22" s="14">
+        <v>1</v>
+      </c>
+      <c r="F22" s="15">
         <v>3.588</v>
       </c>
-      <c r="G22" s="12">
-        <v>0</v>
-      </c>
-      <c r="H22" s="10">
-        <v>1</v>
-      </c>
-      <c r="I22" s="11">
+      <c r="G22" s="16">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>1</v>
+      </c>
+      <c r="I22" s="15">
         <v>3.994</v>
       </c>
-      <c r="J22" s="12">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>0.274</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
+      <c r="J22" s="16">
+        <v>0</v>
+      </c>
+      <c r="K22" s="17">
+        <v>1</v>
+      </c>
+      <c r="L22" s="18">
+        <v>1.402</v>
+      </c>
+      <c r="M22" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="12">
+        <v>21</v>
+      </c>
+      <c r="B23" s="12">
+        <v>1</v>
+      </c>
+      <c r="C23" s="12">
+        <v>9.161</v>
+      </c>
+      <c r="D23" s="12">
+        <v>0</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="12">
+        <v>4.772</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>1</v>
+      </c>
+      <c r="I23" s="9">
+        <v>1.039</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="12">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12">
+        <v>8.047</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
